--- a/resources/one-person-ai-business/files/opab-basics-margin.xlsx
+++ b/resources/one-person-ai-business/files/opab-basics-margin.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,11 +60,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,8 +107,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -520,7 +513,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Platform fee %  (your route — e.g. 2.9 processor, 5 MoR, 10 store)</t>
+          <t>Platform fee %  (your route — e.g. 2.9 processor, 5 merchant of record)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -547,7 +540,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
@@ -603,7 +595,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -625,7 +616,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -647,7 +637,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -661,10 +650,6 @@
           <t>ePORTS — your ecom source. eports.global.</t>
         </is>
       </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/one-person-ai-business/files/opab-basics-margin.xlsx
+++ b/resources/one-person-ai-business/files/opab-basics-margin.xlsx
@@ -647,7 +647,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
